--- a/output_data/charts/0500000US39089.xlsx
+++ b/output_data/charts/0500000US39089.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.7575348627980207</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>2.305078623274295</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.73290674780741</c:v>
+                  <c:v>2.733841920400904</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.258508729537109</c:v>
+                  <c:v>3.258521196772025</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.870932247682447</c:v>
+                  <c:v>3.902715243074453</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.360238208306723</c:v>
+                  <c:v>4.475318731611638</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.836720786595853</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>3.436197330934173</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>4.103310869540677</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.187734920350814</c:v>
+                  <c:v>4.189131747913823</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.320607040289744</c:v>
+                  <c:v>4.323219532243642</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.46345556075152</c:v>
+                  <c:v>4.483806947811698</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.668096789864684</c:v>
+                  <c:v>4.695979078130108</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.865385239429306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.40710751237067</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>2.126722882589996</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.262506712010024</c:v>
+                  <c:v>2.260676972639209</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.335283105859872</c:v>
+                  <c:v>2.331561613098511</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.422358539872913</c:v>
+                  <c:v>2.423872588634352</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.521274447191882</c:v>
+                  <c:v>2.549852893102321</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.686345985354087</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.283100914679862</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.2951900391705329</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2953284410238053</c:v>
+                  <c:v>0.2947493232510794</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.3094083468039839</c:v>
+                  <c:v>0.3088013951602602</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3108409209693835</c:v>
+                  <c:v>0.3078631548276791</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.3024000960693446</c:v>
+                  <c:v>0.2963931568050561</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2947571093251414</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.664417453891138</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>2.303385372571596</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.336898156434581</c:v>
+                  <c:v>2.337300610751918</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.440826348037174</c:v>
+                  <c:v>2.44041965887443</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.440513850301213</c:v>
+                  <c:v>2.440915013276599</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.455226772779624</c:v>
+                  <c:v>2.453960989430097</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.470010492271415</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>92.45164192532613</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>88.8663122128529</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>88.18462502237337</c:v>
+                  <c:v>88.18429942504306</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>87.33536642947212</c:v>
+                  <c:v>87.33747660385113</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>86.49189888042253</c:v>
+                  <c:v>86.44082705237523</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>85.69276368578774</c:v>
+                  <c:v>85.52849515092078</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>84.8467803870242</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>2.73290674780741</v>
+        <v>2.733841920400904</v>
       </c>
       <c r="C12" s="2">
-        <v>4.187734920350814</v>
+        <v>4.189131747913823</v>
       </c>
       <c r="D12" s="2">
-        <v>2.262506712010024</v>
+        <v>2.260676972639209</v>
       </c>
       <c r="E12" s="2">
-        <v>0.2953284410238053</v>
+        <v>0.2947493232510794</v>
       </c>
       <c r="F12" s="2">
-        <v>2.336898156434581</v>
+        <v>2.337300610751918</v>
       </c>
       <c r="G12" s="2">
-        <v>88.18462502237337</v>
+        <v>88.18429942504306</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>3.258508729537109</v>
+        <v>3.258521196772025</v>
       </c>
       <c r="C13" s="2">
-        <v>4.320607040289744</v>
+        <v>4.323219532243642</v>
       </c>
       <c r="D13" s="2">
-        <v>2.335283105859872</v>
+        <v>2.331561613098511</v>
       </c>
       <c r="E13" s="2">
-        <v>0.3094083468039839</v>
+        <v>0.3088013951602602</v>
       </c>
       <c r="F13" s="2">
-        <v>2.440826348037174</v>
+        <v>2.44041965887443</v>
       </c>
       <c r="G13" s="2">
-        <v>87.33536642947212</v>
+        <v>87.33747660385113</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>3.870932247682447</v>
+        <v>3.902715243074453</v>
       </c>
       <c r="C14" s="2">
-        <v>4.46345556075152</v>
+        <v>4.483806947811698</v>
       </c>
       <c r="D14" s="2">
-        <v>2.422358539872913</v>
+        <v>2.423872588634352</v>
       </c>
       <c r="E14" s="2">
-        <v>0.3108409209693835</v>
+        <v>0.3078631548276791</v>
       </c>
       <c r="F14" s="2">
-        <v>2.440513850301213</v>
+        <v>2.440915013276599</v>
       </c>
       <c r="G14" s="2">
-        <v>86.49189888042253</v>
+        <v>86.44082705237523</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>4.360238208306723</v>
+        <v>4.475318731611638</v>
       </c>
       <c r="C15" s="2">
-        <v>4.668096789864684</v>
+        <v>4.695979078130108</v>
       </c>
       <c r="D15" s="2">
-        <v>2.521274447191882</v>
+        <v>2.549852893102321</v>
       </c>
       <c r="E15" s="2">
-        <v>0.3024000960693446</v>
+        <v>0.2963931568050561</v>
       </c>
       <c r="F15" s="2">
-        <v>2.455226772779624</v>
+        <v>2.453960989430097</v>
       </c>
       <c r="G15" s="2">
-        <v>85.69276368578774</v>
+        <v>85.52849515092078</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>4.836720786595853</v>
+      </c>
+      <c r="C16" s="2">
+        <v>4.865385239429306</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2.686345985354087</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.2947571093251414</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2.470010492271415</v>
+      </c>
+      <c r="G16" s="2">
+        <v>84.8467803870242</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39089.xlsx
+++ b/output_data/charts/0500000US39089.xlsx
@@ -226,34 +226,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.7575348627980207</c:v>
+                  <c:v>0.7576257460784019</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7512186369209606</c:v>
+                  <c:v>0.7507597329568567</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.7987544441528072</c:v>
+                  <c:v>0.7995751511137366</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.843163316165476</c:v>
+                  <c:v>0.8423314595069483</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.8902339740186189</c:v>
+                  <c:v>0.8871967416327253</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.9729324453347861</c:v>
+                  <c:v>0.9694568345534579</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.150052855964592</c:v>
+                  <c:v>1.145976871151733</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.414926060187583</c:v>
+                  <c:v>1.399056544002028</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.853073667925558</c:v>
+                  <c:v>1.828469937267314</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.305078623274295</c:v>
+                  <c:v>2.256561613009012</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.733841920400904</c:v>
@@ -357,34 +357,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>3.436197330934173</c:v>
+                  <c:v>3.434809993701449</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.492329316068064</c:v>
+                  <c:v>3.492976956761025</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.559497959865423</c:v>
+                  <c:v>3.562286307573887</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.59456957729096</c:v>
+                  <c:v>3.599646208914823</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.619340908286432</c:v>
+                  <c:v>3.624343309131692</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.679687911856186</c:v>
+                  <c:v>3.685577131603472</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.774845207532265</c:v>
+                  <c:v>3.773409382940003</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.902410955751194</c:v>
+                  <c:v>3.889596064901478</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.946739773399463</c:v>
+                  <c:v>3.931324217549212</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.103310869540677</c:v>
+                  <c:v>4.056835272698488</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>4.189131747913823</c:v>
@@ -488,34 +488,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.40710751237067</c:v>
+                  <c:v>1.407276326444918</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.499446753790484</c:v>
+                  <c:v>1.492546242013831</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.537855830489871</c:v>
+                  <c:v>1.52575646372972</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.605036432250255</c:v>
+                  <c:v>1.587904618873211</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.670737319032954</c:v>
+                  <c:v>1.650433858686028</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.760767568137488</c:v>
+                  <c:v>1.739629918352275</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.849377925955183</c:v>
+                  <c:v>1.829144209357357</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.979975832901778</c:v>
+                  <c:v>1.947965924995824</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.033375801974792</c:v>
+                  <c:v>1.998679311875946</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.126722882589996</c:v>
+                  <c:v>2.07732582465425</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.260676972639209</c:v>
@@ -619,34 +619,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.283100914679862</c:v>
+                  <c:v>0.2819351549143697</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.282903196865935</c:v>
+                  <c:v>0.282955660309636</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2875277386718843</c:v>
+                  <c:v>0.2899951667472209</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2818455842213942</c:v>
+                  <c:v>0.2867132452021536</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2819959175486413</c:v>
+                  <c:v>0.2874682722389469</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2788174858394691</c:v>
+                  <c:v>0.284272409164708</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2735731793733954</c:v>
+                  <c:v>0.2819882204508323</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2888543644628575</c:v>
+                  <c:v>0.2989338601634632</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2889384356372571</c:v>
+                  <c:v>0.3022781870139924</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2951900391705329</c:v>
+                  <c:v>0.3075844443690561</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.2947493232510794</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.664417453891138</c:v>
+                  <c:v>1.660418103836118</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.735099733843715</c:v>
+                  <c:v>1.724055418630806</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.814646018754922</c:v>
+                  <c:v>1.797253996384011</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.888662093845679</c:v>
+                  <c:v>1.864526507618974</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.94919353887178</c:v>
+                  <c:v>1.919603329201346</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.992724972323264</c:v>
+                  <c:v>1.955325272110239</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.075903488493663</c:v>
+                  <c:v>2.02682667317856</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.105989987916451</c:v>
+                  <c:v>2.051642408289511</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.196045866132775</c:v>
+                  <c:v>2.139856318240297</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.303385372571596</c:v>
+                  <c:v>2.245818773959358</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.337300610751918</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>92.45164192532613</c:v>
+                  <c:v>92.45793467502475</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>92.23900236251083</c:v>
+                  <c:v>92.25670598932784</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>92.0017180080651</c:v>
+                  <c:v>92.02513291445142</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>91.78672299622623</c:v>
+                  <c:v>91.81887795988389</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>91.58849834224158</c:v>
+                  <c:v>91.63095448910926</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>91.31506961650881</c:v>
+                  <c:v>91.36573843421584</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>90.8762473426809</c:v>
+                  <c:v>90.94265464292151</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>90.30784279878013</c:v>
+                  <c:v>90.4128051976477</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>89.68182645493016</c:v>
+                  <c:v>89.79939202805323</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>88.8663122128529</c:v>
+                  <c:v>89.05587407130983</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>88.18429942504306</c:v>
@@ -1396,22 +1396,22 @@
         <v>2010</v>
       </c>
       <c r="B2" s="2">
-        <v>0.7575348627980207</v>
+        <v>0.7576257460784019</v>
       </c>
       <c r="C2" s="2">
-        <v>3.436197330934173</v>
+        <v>3.434809993701449</v>
       </c>
       <c r="D2" s="2">
-        <v>1.40710751237067</v>
+        <v>1.407276326444918</v>
       </c>
       <c r="E2" s="2">
-        <v>0.283100914679862</v>
+        <v>0.2819351549143697</v>
       </c>
       <c r="F2" s="2">
-        <v>1.664417453891138</v>
+        <v>1.660418103836118</v>
       </c>
       <c r="G2" s="2">
-        <v>92.45164192532613</v>
+        <v>92.45793467502475</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>0.7512186369209606</v>
+        <v>0.7507597329568567</v>
       </c>
       <c r="C3" s="2">
-        <v>3.492329316068064</v>
+        <v>3.492976956761025</v>
       </c>
       <c r="D3" s="2">
-        <v>1.499446753790484</v>
+        <v>1.492546242013831</v>
       </c>
       <c r="E3" s="2">
-        <v>0.282903196865935</v>
+        <v>0.282955660309636</v>
       </c>
       <c r="F3" s="2">
-        <v>1.735099733843715</v>
+        <v>1.724055418630806</v>
       </c>
       <c r="G3" s="2">
-        <v>92.23900236251083</v>
+        <v>92.25670598932784</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>0.7987544441528072</v>
+        <v>0.7995751511137366</v>
       </c>
       <c r="C4" s="2">
-        <v>3.559497959865423</v>
+        <v>3.562286307573887</v>
       </c>
       <c r="D4" s="2">
-        <v>1.537855830489871</v>
+        <v>1.52575646372972</v>
       </c>
       <c r="E4" s="2">
-        <v>0.2875277386718843</v>
+        <v>0.2899951667472209</v>
       </c>
       <c r="F4" s="2">
-        <v>1.814646018754922</v>
+        <v>1.797253996384011</v>
       </c>
       <c r="G4" s="2">
-        <v>92.0017180080651</v>
+        <v>92.02513291445142</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>0.843163316165476</v>
+        <v>0.8423314595069483</v>
       </c>
       <c r="C5" s="2">
-        <v>3.59456957729096</v>
+        <v>3.599646208914823</v>
       </c>
       <c r="D5" s="2">
-        <v>1.605036432250255</v>
+        <v>1.587904618873211</v>
       </c>
       <c r="E5" s="2">
-        <v>0.2818455842213942</v>
+        <v>0.2867132452021536</v>
       </c>
       <c r="F5" s="2">
-        <v>1.888662093845679</v>
+        <v>1.864526507618974</v>
       </c>
       <c r="G5" s="2">
-        <v>91.78672299622623</v>
+        <v>91.81887795988389</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>0.8902339740186189</v>
+        <v>0.8871967416327253</v>
       </c>
       <c r="C6" s="2">
-        <v>3.619340908286432</v>
+        <v>3.624343309131692</v>
       </c>
       <c r="D6" s="2">
-        <v>1.670737319032954</v>
+        <v>1.650433858686028</v>
       </c>
       <c r="E6" s="2">
-        <v>0.2819959175486413</v>
+        <v>0.2874682722389469</v>
       </c>
       <c r="F6" s="2">
-        <v>1.94919353887178</v>
+        <v>1.919603329201346</v>
       </c>
       <c r="G6" s="2">
-        <v>91.58849834224158</v>
+        <v>91.63095448910926</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>0.9729324453347861</v>
+        <v>0.9694568345534579</v>
       </c>
       <c r="C7" s="2">
-        <v>3.679687911856186</v>
+        <v>3.685577131603472</v>
       </c>
       <c r="D7" s="2">
-        <v>1.760767568137488</v>
+        <v>1.739629918352275</v>
       </c>
       <c r="E7" s="2">
-        <v>0.2788174858394691</v>
+        <v>0.284272409164708</v>
       </c>
       <c r="F7" s="2">
-        <v>1.992724972323264</v>
+        <v>1.955325272110239</v>
       </c>
       <c r="G7" s="2">
-        <v>91.31506961650881</v>
+        <v>91.36573843421584</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>1.150052855964592</v>
+        <v>1.145976871151733</v>
       </c>
       <c r="C8" s="2">
-        <v>3.774845207532265</v>
+        <v>3.773409382940003</v>
       </c>
       <c r="D8" s="2">
-        <v>1.849377925955183</v>
+        <v>1.829144209357357</v>
       </c>
       <c r="E8" s="2">
-        <v>0.2735731793733954</v>
+        <v>0.2819882204508323</v>
       </c>
       <c r="F8" s="2">
-        <v>2.075903488493663</v>
+        <v>2.02682667317856</v>
       </c>
       <c r="G8" s="2">
-        <v>90.8762473426809</v>
+        <v>90.94265464292151</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>1.414926060187583</v>
+        <v>1.399056544002028</v>
       </c>
       <c r="C9" s="2">
-        <v>3.902410955751194</v>
+        <v>3.889596064901478</v>
       </c>
       <c r="D9" s="2">
-        <v>1.979975832901778</v>
+        <v>1.947965924995824</v>
       </c>
       <c r="E9" s="2">
-        <v>0.2888543644628575</v>
+        <v>0.2989338601634632</v>
       </c>
       <c r="F9" s="2">
-        <v>2.105989987916451</v>
+        <v>2.051642408289511</v>
       </c>
       <c r="G9" s="2">
-        <v>90.30784279878013</v>
+        <v>90.4128051976477</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>1.853073667925558</v>
+        <v>1.828469937267314</v>
       </c>
       <c r="C10" s="2">
-        <v>3.946739773399463</v>
+        <v>3.931324217549212</v>
       </c>
       <c r="D10" s="2">
-        <v>2.033375801974792</v>
+        <v>1.998679311875946</v>
       </c>
       <c r="E10" s="2">
-        <v>0.2889384356372571</v>
+        <v>0.3022781870139924</v>
       </c>
       <c r="F10" s="2">
-        <v>2.196045866132775</v>
+        <v>2.139856318240297</v>
       </c>
       <c r="G10" s="2">
-        <v>89.68182645493016</v>
+        <v>89.79939202805323</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>2.305078623274295</v>
+        <v>2.256561613009012</v>
       </c>
       <c r="C11" s="2">
-        <v>4.103310869540677</v>
+        <v>4.056835272698488</v>
       </c>
       <c r="D11" s="2">
-        <v>2.126722882589996</v>
+        <v>2.07732582465425</v>
       </c>
       <c r="E11" s="2">
-        <v>0.2951900391705329</v>
+        <v>0.3075844443690561</v>
       </c>
       <c r="F11" s="2">
-        <v>2.303385372571596</v>
+        <v>2.245818773959358</v>
       </c>
       <c r="G11" s="2">
-        <v>88.8663122128529</v>
+        <v>89.05587407130983</v>
       </c>
     </row>
     <row r="12" spans="1:7">
